--- a/YER/Kashish_Taneja_YER.xlsx
+++ b/YER/Kashish_Taneja_YER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kashtane\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kashtane\Documents\YER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FF8E2B-E3C2-4300-B9A3-61CD1F491DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EA0A9F-581B-454F-AA2B-CFD95C2E11A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="743" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="743" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Training period(Nov24-Dec24)" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="304">
   <si>
     <t>Training Area</t>
   </si>
@@ -907,6 +907,36 @@
   </si>
   <si>
     <t xml:space="preserve">[Pilot] Old github links in github repo wiki </t>
+  </si>
+  <si>
+    <t>extract metadata of all repositories and their utilities details from gitlab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">had to extract details about all the utilities and their count if present which are there in a certain gitlab repository </t>
+  </si>
+  <si>
+    <t>Prepared a custom script, which ha input as the gitlab repository name and gave thenoutput csv containing all about every data presnt or not present in a gitlab repo.</t>
+  </si>
+  <si>
+    <t>extract metadata of all repositories and their utilities details from github</t>
+  </si>
+  <si>
+    <t xml:space="preserve">had to extract details about all the utilities and their count if present which are there in a certain github repository </t>
+  </si>
+  <si>
+    <t>Prepared a custom script, which ha input as the github repository name and gave the output csv containing all about every data presnt or not present in a github repo.</t>
+  </si>
+  <si>
+    <t>Completion_Date</t>
+  </si>
+  <si>
+    <t>aws_cloud_beginnner_ocean_certificate</t>
+  </si>
+  <si>
+    <t>Achieved internal certification demonstrating AWS Cloud Beginner-level knowledge</t>
+  </si>
+  <si>
+    <t>Global Insurance Industry L2 Certification</t>
   </si>
 </sst>
 </file>
@@ -942,8 +972,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2339,10 +2370,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="55" customWidth="1"/>
+    <col min="1" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -2496,6 +2529,34 @@
       </c>
       <c r="E9" t="s">
         <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>294</v>
+      </c>
+      <c r="B10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D10" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>297</v>
+      </c>
+      <c r="B11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" t="s">
+        <v>299</v>
+      </c>
+      <c r="D11" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2505,318 +2566,420 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="40" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>91</v>
       </c>
       <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>92</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>93</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1">
+        <v>46054</v>
+      </c>
+      <c r="C2" t="s">
         <v>94</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>95</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>97</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1">
+        <v>45689</v>
+      </c>
+      <c r="C3" t="s">
         <v>98</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>95</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>100</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1">
+        <v>45870</v>
+      </c>
+      <c r="C4" t="s">
         <v>101</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>102</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>104</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1">
+        <v>45870</v>
+      </c>
+      <c r="C5" t="s">
         <v>105</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>106</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>108</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1">
+        <v>45931</v>
+      </c>
+      <c r="C6" t="s">
         <v>109</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>106</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>111</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1">
+        <v>46054</v>
+      </c>
+      <c r="C7" t="s">
         <v>112</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>106</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>114</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1">
+        <v>45597</v>
+      </c>
+      <c r="C8" t="s">
         <v>115</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>95</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>117</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1">
+        <v>46054</v>
+      </c>
+      <c r="C9" t="s">
         <v>118</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>95</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>120</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1">
+        <v>46054</v>
+      </c>
+      <c r="C10" t="s">
         <v>121</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>95</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>123</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1">
+        <v>46054</v>
+      </c>
+      <c r="C11" t="s">
         <v>124</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>95</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>126</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1">
+        <v>46023</v>
+      </c>
+      <c r="C12" t="s">
         <v>127</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>106</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45717</v>
+      </c>
+      <c r="C13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>129</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" s="1">
+        <v>45839</v>
+      </c>
+      <c r="C14" t="s">
         <v>130</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D14" t="s">
         <v>131</v>
       </c>
-      <c r="D13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="E14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>133</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" s="1">
+        <v>46023</v>
+      </c>
+      <c r="C15" t="s">
         <v>134</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D15" t="s">
         <v>95</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>136</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" s="1">
+        <v>46054</v>
+      </c>
+      <c r="C16" t="s">
         <v>137</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D16" t="s">
         <v>95</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E16" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>139</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" s="1">
+        <v>46023</v>
+      </c>
+      <c r="C17" t="s">
         <v>140</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D17" t="s">
         <v>106</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E17" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>142</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" s="1">
+        <v>46023</v>
+      </c>
+      <c r="C18" t="s">
         <v>143</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D18" t="s">
         <v>106</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E18" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>145</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" s="1">
+        <v>45689</v>
+      </c>
+      <c r="C19" t="s">
         <v>146</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D19" t="s">
         <v>95</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E19" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>148</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" s="1">
+        <v>45658</v>
+      </c>
+      <c r="C20" t="s">
         <v>149</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D20" t="s">
         <v>106</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E20" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>151</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C21" t="s">
         <v>152</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D21" t="s">
         <v>95</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E21" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>154</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C22" t="s">
         <v>155</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D22" t="s">
         <v>156</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E22" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>158</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C23" t="s">
         <v>159</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D23" t="s">
         <v>156</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E23" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>303</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/YER/Kashish_Taneja_YER.xlsx
+++ b/YER/Kashish_Taneja_YER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kashtane\Documents\YER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EA0A9F-581B-454F-AA2B-CFD95C2E11A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A286AB-8B70-468B-98B9-15C1DD7D2224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="743" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2593,325 +2593,325 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1">
-        <v>46054</v>
+        <v>45597</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
         <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="B3" s="1">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B4" s="1">
-        <v>45870</v>
+        <v>45689</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="B5" s="1">
-        <v>45870</v>
+        <v>45689</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>301</v>
       </c>
       <c r="B6" s="1">
-        <v>45931</v>
+        <v>45717</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B7" s="1">
-        <v>46054</v>
+        <v>45839</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B8" s="1">
-        <v>45597</v>
+        <v>45870</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B9" s="1">
-        <v>46054</v>
+        <v>45870</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B10" s="1">
-        <v>46054</v>
+        <v>45931</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B11" s="1">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B12" s="1">
         <v>46023</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>301</v>
+        <v>139</v>
       </c>
       <c r="B13" s="1">
-        <v>45717</v>
+        <v>46023</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B14" s="1">
-        <v>45839</v>
+        <v>46023</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>302</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="B15" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
         <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>46054</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B17" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="B18" s="1">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="B19" s="1">
-        <v>45689</v>
+        <v>46054</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
         <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B20" s="1">
-        <v>45658</v>
+        <v>46054</v>
       </c>
       <c r="C20" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -2983,6 +2983,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E24">
+    <sortCondition ref="B2:B24"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
